--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,22 +14346,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI127"/>
+  <dimension ref="A1:BI128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Notts County</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46109.39583333334</v>
+        <v>46109.375</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Notts County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46109.41666666666</v>
+        <v>46109.39583333334</v>
       </c>
     </row>
     <row r="26">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46109.4375</v>
+        <v>46109.41666666666</v>
       </c>
     </row>
     <row r="29">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46109.45833333334</v>
+        <v>46109.4375</v>
       </c>
     </row>
     <row r="36">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46109.47916666666</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.47916666666</v>
       </c>
     </row>
     <row r="39">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46109.51041666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="67">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.51041666666</v>
       </c>
     </row>
     <row r="69">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14341,27 +14341,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="72">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="77">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="84">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="89">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46109.61458333334</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46109.625</v>
+        <v>46109.61458333334</v>
       </c>
     </row>
     <row r="93">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.625</v>
       </c>
     </row>
     <row r="95">
@@ -19463,27 +19463,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="98">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46109.6875</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="104">
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.6875</v>
       </c>
     </row>
     <row r="105">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46109.75</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="110">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46109.8125</v>
+        <v>46109.75</v>
       </c>
     </row>
     <row r="112">
@@ -22418,12 +22418,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.8125</v>
       </c>
     </row>
     <row r="113">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="119">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.85416666666</v>
       </c>
     </row>
     <row r="122">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24979,27 +24979,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46109.90625</v>
+        <v>46109.875</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>San Diego Wave</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46109.95833333334</v>
+        <v>46109.90625</v>
       </c>
     </row>
     <row r="127">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Sacramento Republic</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>El Paso Locomotive</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25561,6 +25561,203 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
+        <v>46109.95833333334</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI128" s="3" t="n">
         <v>46109.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>9.25</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>3.16</v>
+        <v>1.77</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>2.21</v>
+        <v>4.29</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>3.43</v>
+        <v>2.88</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R47" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="R48" t="n">
-        <v>4.29</v>
+        <v>3.43</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="R52" t="n">
-        <v>6.26</v>
+        <v>5.36</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.49</v>
+        <v>2.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.44</v>
+        <v>3.42</v>
       </c>
       <c r="R53" t="n">
-        <v>2.63</v>
+        <v>2.78</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="R55" t="n">
-        <v>5.36</v>
+        <v>6.26</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.34</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.77</v>
+        <v>2.69</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>4.29</v>
+        <v>2.5</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.84</v>
+        <v>1.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.32</v>
+        <v>4.15</v>
       </c>
       <c r="R47" t="n">
-        <v>2.38</v>
+        <v>6.26</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="R62" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P123" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.69</v>
+        <v>2.49</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R41" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="R42" t="n">
-        <v>3.43</v>
+        <v>3.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="R46" t="n">
-        <v>2.88</v>
+        <v>6.26</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.16</v>
+        <v>2.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R56" t="n">
-        <v>2.21</v>
+        <v>2.78</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="R60" t="n">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.28</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="R66" t="n">
-        <v>3.03</v>
+        <v>3.43</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,17 +24437,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,7 +25028,7 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="R42" t="n">
-        <v>3.03</v>
+        <v>2.63</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.9</v>
+        <v>4.15</v>
       </c>
       <c r="R48" t="n">
-        <v>5.36</v>
+        <v>6.26</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.69</v>
+        <v>1.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="R50" t="n">
-        <v>2.5</v>
+        <v>5.36</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>2.21</v>
+        <v>3.28</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R56" t="n">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.24</v>
+        <v>2.69</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R57" t="n">
-        <v>3.28</v>
+        <v>2.5</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.84</v>
+        <v>2.38</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.32</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="R63" t="n">
-        <v>2.88</v>
+        <v>3.03</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="R66" t="n">
-        <v>3.43</v>
+        <v>2.38</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,17 +24437,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,17 +25028,17 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.14</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.34</v>
+        <v>3.65</v>
       </c>
       <c r="R40" t="n">
-        <v>3.33</v>
+        <v>4.29</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>2.63</v>
+        <v>2.21</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.16</v>
+        <v>1.5</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.3</v>
+        <v>4.15</v>
       </c>
       <c r="R56" t="n">
-        <v>2.21</v>
+        <v>6.26</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R57" t="n">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>3.44</v>
       </c>
       <c r="R60" t="n">
-        <v>2.78</v>
+        <v>2.63</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R61" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="R66" t="n">
-        <v>2.38</v>
+        <v>5.36</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,22 +15331,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,7 +24634,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P123" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R43" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="R44" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,17 +10450,17 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,22 +10800,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="R54" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R57" t="n">
-        <v>3.43</v>
+        <v>5.36</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="R60" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R61" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R66" t="n">
-        <v>5.36</v>
+        <v>3.43</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24634,17 +24634,17 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,17 +24831,17 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>9.25</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="R43" t="n">
-        <v>2.78</v>
+        <v>3.33</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R50" t="n">
-        <v>4.29</v>
+        <v>3.03</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.14</v>
+        <v>2.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.34</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>3.33</v>
+        <v>2.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.84</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.32</v>
+        <v>3.9</v>
       </c>
       <c r="R54" t="n">
-        <v>2.38</v>
+        <v>5.36</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="R57" t="n">
-        <v>5.36</v>
+        <v>2.88</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.49</v>
+        <v>2.24</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.63</v>
+        <v>3.28</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF58" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R60" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R64" t="n">
-        <v>2.88</v>
+        <v>3.43</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,17 +24437,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="Q123" t="n">
         <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>4.5</v>
+        <v>3.51</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>9.25</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.84</v>
+        <v>2.49</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.32</v>
+        <v>3.44</v>
       </c>
       <c r="R39" t="n">
-        <v>2.38</v>
+        <v>2.63</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.89</v>
+        <v>1.81</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="R43" t="n">
-        <v>3.33</v>
+        <v>3.03</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="R50" t="n">
-        <v>3.03</v>
+        <v>3.33</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10302,10 +10302,10 @@
         <v>0</v>
       </c>
       <c r="AE50" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF50" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3.16</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R52" t="n">
-        <v>2.21</v>
+        <v>3.28</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="R58" t="n">
-        <v>3.28</v>
+        <v>5.41</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="R60" t="n">
-        <v>2.78</v>
+        <v>3.43</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="R64" t="n">
-        <v>3.43</v>
+        <v>2.42</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,17 +24437,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,17 +25028,17 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>9.25</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.63</v>
+        <v>2.88</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,7 +9071,7 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="R50" t="n">
-        <v>3.33</v>
+        <v>6.26</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>3.42</v>
       </c>
       <c r="R53" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q55" t="n">
-        <v>4.15</v>
+        <v>3.24</v>
       </c>
       <c r="R55" t="n">
-        <v>6.26</v>
+        <v>2.42</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.63</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.29</v>
+        <v>3.34</v>
       </c>
       <c r="R58" t="n">
-        <v>5.41</v>
+        <v>3.33</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="R60" t="n">
-        <v>3.43</v>
+        <v>2.38</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.8</v>
+        <v>1.77</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.24</v>
+        <v>3.65</v>
       </c>
       <c r="R64" t="n">
-        <v>2.42</v>
+        <v>4.29</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R66" t="n">
-        <v>5.36</v>
+        <v>3.43</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,22 +15134,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,17 +24437,17 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,17 +25028,17 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.79</v>
+        <v>2.02</v>
       </c>
       <c r="Q123" t="n">
         <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>4.5</v>
+        <v>3.51</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="Q125" t="n">
         <v>3.4</v>
       </c>
       <c r="R125" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="R54" t="n">
-        <v>5.36</v>
+        <v>3.28</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.24</v>
+        <v>3.55</v>
       </c>
       <c r="R55" t="n">
-        <v>2.42</v>
+        <v>3.43</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11632,17 +11632,17 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>2.69</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R63" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="R64" t="n">
-        <v>4.29</v>
+        <v>5.36</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.55</v>
+        <v>4.15</v>
       </c>
       <c r="R66" t="n">
-        <v>3.43</v>
+        <v>6.26</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,17 +24831,17 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="R12" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.63</v>
+        <v>2.69</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="R40" t="n">
-        <v>5.41</v>
+        <v>2.5</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10056,17 +10056,17 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.77</v>
+        <v>2.84</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.65</v>
+        <v>3.32</v>
       </c>
       <c r="R51" t="n">
-        <v>4.29</v>
+        <v>2.38</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.42</v>
+        <v>3.35</v>
       </c>
       <c r="R53" t="n">
-        <v>2.78</v>
+        <v>3.03</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="R54" t="n">
-        <v>3.28</v>
+        <v>5.41</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="R55" t="n">
-        <v>3.43</v>
+        <v>3.33</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="R62" t="n">
-        <v>3.03</v>
+        <v>2.63</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>6.26</v>
+        <v>2.88</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19358,10 +19358,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19555,10 +19555,10 @@
         <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD97" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19752,10 +19752,10 @@
         <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD98" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22707,10 +22707,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,17 +25028,17 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="R12" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.96</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>2.79</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>3.43</v>
       </c>
       <c r="R26" t="n">
-        <v>9.25</v>
+        <v>3.43</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>9.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>3.16</v>
+        <v>2.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="R42" t="n">
-        <v>2.21</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9071,17 +9071,17 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>2.49</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.24</v>
+        <v>3.44</v>
       </c>
       <c r="R47" t="n">
-        <v>2.42</v>
+        <v>2.63</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.77</v>
+        <v>2</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="R48" t="n">
-        <v>4.29</v>
+        <v>3.43</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R49" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.84</v>
+        <v>1.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.32</v>
+        <v>3.29</v>
       </c>
       <c r="R51" t="n">
-        <v>2.38</v>
+        <v>5.41</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.29</v>
+        <v>4.15</v>
       </c>
       <c r="R54" t="n">
-        <v>5.41</v>
+        <v>6.26</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="Q61" t="n">
-        <v>4.15</v>
+        <v>3.9</v>
       </c>
       <c r="R61" t="n">
-        <v>6.26</v>
+        <v>5.36</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
-        <v>10</v>
+        <v>3.73</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF90" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19161,10 +19161,10 @@
         <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R96" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19358,10 +19358,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19555,10 +19555,10 @@
         <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22707,10 +22707,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD116" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q120" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R120" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="Q124" t="n">
         <v>3.4</v>
       </c>
       <c r="R124" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25028,17 +25028,17 @@
       </c>
       <c r="O125" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>3.43</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.1</v>
+        <v>3.29</v>
       </c>
       <c r="R43" t="n">
-        <v>3.28</v>
+        <v>5.41</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R44" t="n">
-        <v>2.88</v>
+        <v>3.43</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.49</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.44</v>
+        <v>3.24</v>
       </c>
       <c r="R47" t="n">
-        <v>2.63</v>
+        <v>2.42</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R48" t="n">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="R51" t="n">
-        <v>5.41</v>
+        <v>2.88</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,22 +13361,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -14543,22 +14543,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,22 +14937,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.8</v>
+        <v>3.5</v>
       </c>
       <c r="R89" t="n">
-        <v>10</v>
+        <v>3.73</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF89" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="R90" t="n">
-        <v>3.73</v>
+        <v>10</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18182,10 +18182,10 @@
         <v>0</v>
       </c>
       <c r="AE90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF90" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG90" t="n">
         <v>0</v>
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R95" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19161,10 +19161,10 @@
         <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD95" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="R96" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19358,10 +19358,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD96" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI128"/>
+  <dimension ref="A1:BI133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>9.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>3.43</v>
       </c>
       <c r="R27" t="n">
-        <v>9.25</v>
+        <v>3.43</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>3.43</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.69</v>
+        <v>1.77</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>2.5</v>
+        <v>4.29</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.94</v>
+        <v>1.84</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.63</v>
+        <v>2.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="R43" t="n">
-        <v>5.41</v>
+        <v>2.38</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="R44" t="n">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.38</v>
+        <v>1.57</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.42</v>
+        <v>4.27</v>
       </c>
       <c r="R46" t="n">
-        <v>2.78</v>
+        <v>4.64</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>3.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>2.42</v>
+        <v>2.21</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.1</v>
+        <v>3.42</v>
       </c>
       <c r="R48" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.3</v>
+        <v>3.44</v>
       </c>
       <c r="R51" t="n">
-        <v>2.88</v>
+        <v>2.63</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10696,10 +10696,10 @@
         <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>1.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.34</v>
+        <v>3.9</v>
       </c>
       <c r="R56" t="n">
-        <v>3.33</v>
+        <v>5.36</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12223,17 +12223,17 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13553,12 +13553,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46109.51041666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="68">
@@ -13750,12 +13750,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,56 +13803,56 @@
         </is>
       </c>
       <c r="P68" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R68" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="S68" t="n">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>0</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
+      </c>
+      <c r="V68" t="n">
+        <v>0</v>
+      </c>
+      <c r="W68" t="n">
+        <v>0</v>
+      </c>
+      <c r="X68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AF68" t="n">
         <v>1.76</v>
       </c>
-      <c r="Q68" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R68" t="n">
-        <v>4.84</v>
-      </c>
-      <c r="S68" t="n">
-        <v>0</v>
-      </c>
-      <c r="T68" t="n">
-        <v>0</v>
-      </c>
-      <c r="U68" t="n">
-        <v>0</v>
-      </c>
-      <c r="V68" t="n">
-        <v>0</v>
-      </c>
-      <c r="W68" t="n">
-        <v>0</v>
-      </c>
-      <c r="X68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AG68" t="n">
         <v>0</v>
       </c>
@@ -13938,7 +13938,7 @@
         <v>0</v>
       </c>
       <c r="BI68" s="3" t="n">
-        <v>46109.51041666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="69">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="BI69" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="70">
@@ -14144,12 +14144,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14332,7 +14332,7 @@
         <v>0</v>
       </c>
       <c r="BI70" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="71">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14529,7 +14529,7 @@
         <v>0</v>
       </c>
       <c r="BI71" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="72">
@@ -14538,27 +14538,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.51041666666</v>
       </c>
     </row>
     <row r="73">
@@ -14735,12 +14735,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.51041666666</v>
       </c>
     </row>
     <row r="74">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="76">
@@ -15326,7 +15326,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="77">
@@ -15523,27 +15523,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="79">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="81">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="82">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="86">
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="87">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="88">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -17985,10 +17985,10 @@
         <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF89" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG89" t="n">
         <v>0</v>
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46109.61458333334</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="93">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46109.625</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="94">
@@ -18872,27 +18872,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46109.625</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="95">
@@ -19069,27 +19069,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19161,10 +19161,10 @@
         <v>0</v>
       </c>
       <c r="AC95" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="96">
@@ -19266,27 +19266,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.81</v>
+        <v>1.21</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.82</v>
+        <v>5.8</v>
       </c>
       <c r="R96" t="n">
-        <v>2.51</v>
+        <v>10</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19358,10 +19358,10 @@
         <v>0</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD96" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="97">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.61458333334</v>
       </c>
     </row>
     <row r="98">
@@ -19660,27 +19660,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19752,10 +19752,10 @@
         <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE98" t="n">
         <v>0</v>
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.625</v>
       </c>
     </row>
     <row r="99">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.625</v>
       </c>
     </row>
     <row r="100">
@@ -20054,12 +20054,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,14 +20107,14 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="Q100" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="R100" t="n">
         <v>2.8</v>
       </c>
-      <c r="R100" t="n">
-        <v>2.52</v>
-      </c>
       <c r="S100" t="n">
         <v>0</v>
       </c>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="101">
@@ -20251,27 +20251,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="102">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="103">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.65</v>
+        <v>3.11</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="R104" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,16 +20934,16 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46109.6875</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="105">
@@ -21039,27 +21039,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="106">
@@ -21236,27 +21236,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.44</v>
+        <v>3.13</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.81</v>
+        <v>2.8</v>
       </c>
       <c r="R106" t="n">
-        <v>2.05</v>
+        <v>2.52</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="107">
@@ -21433,27 +21433,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="108">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="109">
@@ -21827,27 +21827,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.44</v>
+        <v>3.25</v>
       </c>
       <c r="R109" t="n">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.6875</v>
       </c>
     </row>
     <row r="110">
@@ -22024,27 +22024,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46109.75</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="111">
@@ -22221,27 +22221,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.24</v>
+        <v>2.52</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.79</v>
+        <v>3.44</v>
       </c>
       <c r="R111" t="n">
-        <v>3.67</v>
+        <v>2.83</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46109.75</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="112">
@@ -22418,7 +22418,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46109.8125</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="113">
@@ -22615,27 +22615,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="114">
@@ -22812,12 +22812,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="115">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.75</v>
       </c>
     </row>
     <row r="116">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23298,10 +23298,10 @@
         <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="n">
         <v>0</v>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.75</v>
       </c>
     </row>
     <row r="117">
@@ -23403,7 +23403,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.8125</v>
       </c>
     </row>
     <row r="118">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23797,12 +23797,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="120">
@@ -23994,12 +23994,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="121">
@@ -24191,12 +24191,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24283,10 +24283,10 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="122">
@@ -24388,27 +24388,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="123">
@@ -24585,27 +24585,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="124">
@@ -24782,7 +24782,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="R124" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.85416666666</v>
       </c>
     </row>
     <row r="125">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.85416666666</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46109.90625</v>
+        <v>46109.85416666666</v>
       </c>
     </row>
     <row r="127">
@@ -25373,7 +25373,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q127" t="n">
-        <v>2.58</v>
+        <v>3.4</v>
       </c>
       <c r="R127" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46109.95833333334</v>
+        <v>46109.875</v>
       </c>
     </row>
     <row r="128">
@@ -25570,7 +25570,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,141 +25623,1126 @@
         </is>
       </c>
       <c r="P128" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R128" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI128" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Chayka</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI129" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Athletic Carpi</t>
+        </is>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI130" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI131" s="3" t="n">
+        <v>46109.90625</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P132" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R132" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI132" s="3" t="n">
+        <v>46109.95833333334</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P133" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q128" t="n">
+      <c r="Q133" t="n">
         <v>2.94</v>
       </c>
-      <c r="R128" t="n">
+      <c r="R133" t="n">
         <v>3.01</v>
       </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI128" s="3" t="n">
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI133" s="3" t="n">
         <v>46109.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.77</v>
+        <v>1.63</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>3.29</v>
       </c>
       <c r="R39" t="n">
-        <v>4.29</v>
+        <v>5.41</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="R55" t="n">
-        <v>3.03</v>
+        <v>4.29</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="R56" t="n">
-        <v>5.36</v>
+        <v>3.03</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>6.26</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.69</v>
+        <v>2.4</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R68" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.29</v>
+        <v>4.34</v>
       </c>
       <c r="R70" t="n">
-        <v>5.41</v>
+        <v>6.11</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="R72" t="n">
-        <v>4.84</v>
+        <v>3.38</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="R73" t="n">
-        <v>3.38</v>
+        <v>4.84</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.38</v>
+        <v>2.96</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3801,10 +3801,10 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>2.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>9.25</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.43</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>3.43</v>
+        <v>9.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8677,17 +8677,17 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.24</v>
+        <v>2.84</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.1</v>
+        <v>3.32</v>
       </c>
       <c r="R44" t="n">
-        <v>3.28</v>
+        <v>2.38</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.57</v>
+        <v>2.24</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.27</v>
+        <v>3.1</v>
       </c>
       <c r="R46" t="n">
-        <v>4.64</v>
+        <v>3.28</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.38</v>
+        <v>3.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.42</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.28</v>
+        <v>1.63</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="R50" t="n">
-        <v>2.98</v>
+        <v>5.41</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10499,10 +10499,10 @@
         <v>0</v>
       </c>
       <c r="AE51" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF51" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG51" t="n">
         <v>0</v>
@@ -10603,22 +10603,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.77</v>
+        <v>2.4</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="R55" t="n">
-        <v>4.29</v>
+        <v>2.88</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11484,10 +11484,10 @@
         <v>0</v>
       </c>
       <c r="AE56" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF56" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.24</v>
+        <v>4.15</v>
       </c>
       <c r="R62" t="n">
-        <v>2.42</v>
+        <v>6.26</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="R63" t="n">
-        <v>3.43</v>
+        <v>2.78</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.6</v>
+        <v>2.49</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.9</v>
+        <v>3.44</v>
       </c>
       <c r="R64" t="n">
-        <v>5.36</v>
+        <v>2.63</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="R72" t="n">
-        <v>3.38</v>
+        <v>4.84</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="R73" t="n">
-        <v>4.84</v>
+        <v>3.38</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD101" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R102" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21525,10 +21525,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.54</v>
+        <v>3.44</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>3.81</v>
       </c>
       <c r="R114" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24283,10 +24283,10 @@
         <v>0</v>
       </c>
       <c r="AC121" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD121" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24480,10 +24480,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,17 +25619,17 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q129" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R129" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26013,17 +26013,17 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.59</v>
+        <v>2.46</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>2.86</v>
       </c>
       <c r="R10" t="n">
-        <v>2.44</v>
+        <v>2.91</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>3.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.38</v>
+        <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="R26" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>3.43</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,17 +8480,17 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.29</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8874,17 +8874,17 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.84</v>
+        <v>3.16</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="R44" t="n">
-        <v>2.38</v>
+        <v>2.21</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="R46" t="n">
-        <v>3.28</v>
+        <v>6.26</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.28</v>
+        <v>2.69</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="R54" t="n">
-        <v>2.98</v>
+        <v>2.5</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.4</v>
+        <v>1.63</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="R55" t="n">
-        <v>2.88</v>
+        <v>5.41</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>1.44</v>
+        <v>2.28</v>
       </c>
       <c r="Q60" t="n">
-        <v>4.34</v>
+        <v>3.35</v>
       </c>
       <c r="R60" t="n">
-        <v>6.11</v>
+        <v>3.03</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>3.03</v>
+        <v>3.28</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.38</v>
+        <v>2.28</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.42</v>
+        <v>3.31</v>
       </c>
       <c r="R63" t="n">
-        <v>2.78</v>
+        <v>2.98</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.49</v>
+        <v>1.57</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.44</v>
+        <v>4.27</v>
       </c>
       <c r="R64" t="n">
-        <v>2.63</v>
+        <v>4.64</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="R72" t="n">
-        <v>4.84</v>
+        <v>3.38</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="R73" t="n">
-        <v>3.38</v>
+        <v>4.84</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,22 +16119,22 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.05</v>
+        <v>1.21</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.5</v>
+        <v>5.8</v>
       </c>
       <c r="R94" t="n">
-        <v>3.73</v>
+        <v>10</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18970,10 +18970,10 @@
         <v>0</v>
       </c>
       <c r="AE94" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF94" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD100" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R101" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21525,10 +21525,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3.13</v>
+        <v>2.69</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="R108" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21722,10 +21722,10 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="R113" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22713,10 +22713,10 @@
         <v>0</v>
       </c>
       <c r="AE113" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG113" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,17 +25619,17 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="Q129" t="n">
         <v>3.4</v>
       </c>
       <c r="R129" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.24</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>2.44</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.43</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>3.43</v>
+        <v>9.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>3.43</v>
       </c>
       <c r="R27" t="n">
-        <v>9.25</v>
+        <v>3.43</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="R39" t="n">
-        <v>4.29</v>
+        <v>6.26</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8480,7 +8480,7 @@
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -8923,10 +8923,10 @@
         <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.15</v>
+        <v>4.34</v>
       </c>
       <c r="R46" t="n">
-        <v>6.26</v>
+        <v>6.11</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>4.45</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.96</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>1.64</v>
+        <v>4.79</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.34</v>
+        <v>3.24</v>
       </c>
       <c r="R51" t="n">
-        <v>3.33</v>
+        <v>2.42</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.55</v>
+        <v>3.29</v>
       </c>
       <c r="R53" t="n">
-        <v>3.43</v>
+        <v>5.41</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="R60" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>3.34</v>
       </c>
       <c r="R61" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.4</v>
+        <v>1.77</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="R66" t="n">
-        <v>2.88</v>
+        <v>4.29</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R69" t="n">
-        <v>2.42</v>
+        <v>3.28</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>1.6</v>
+        <v>2.28</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="R70" t="n">
-        <v>5.36</v>
+        <v>3.03</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.82</v>
+        <v>1.93</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,22 +16316,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R103" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21722,10 +21722,10 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.97</v>
+        <v>3.05</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="R119" t="n">
-        <v>3.74</v>
+        <v>2.58</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23889,10 +23889,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD119" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24480,10 +24480,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="R10" t="n">
-        <v>2.91</v>
+        <v>2.44</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.18</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.44</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>3.43</v>
       </c>
       <c r="R26" t="n">
-        <v>9.25</v>
+        <v>3.43</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.43</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>3.43</v>
+        <v>9.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5771,10 +5771,10 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R42" t="n">
-        <v>5.36</v>
+        <v>4.79</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="R46" t="n">
-        <v>6.11</v>
+        <v>6.26</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>3.16</v>
+        <v>1.6</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="R48" t="n">
-        <v>2.21</v>
+        <v>5.36</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="R49" t="n">
-        <v>4.79</v>
+        <v>5.41</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="R50" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.29</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>5.41</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="R57" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11681,10 +11681,10 @@
         <v>0</v>
       </c>
       <c r="AE57" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF57" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.49</v>
+        <v>1.44</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.44</v>
+        <v>4.34</v>
       </c>
       <c r="R62" t="n">
-        <v>2.63</v>
+        <v>6.11</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,17 +13602,17 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.28</v>
+        <v>2.69</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="R70" t="n">
-        <v>3.03</v>
+        <v>2.5</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2</v>
+        <v>3.16</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>3.43</v>
+        <v>2.21</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.31</v>
+        <v>3.75</v>
       </c>
       <c r="R72" t="n">
-        <v>3.38</v>
+        <v>4.84</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>1.76</v>
+        <v>2.25</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.75</v>
+        <v>3.31</v>
       </c>
       <c r="R73" t="n">
-        <v>4.84</v>
+        <v>3.38</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,22 +15528,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,22 +15922,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R100" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20343,10 +20343,10 @@
         <v>0</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD101" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20737,10 +20737,10 @@
         <v>0</v>
       </c>
       <c r="AC103" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R107" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21525,10 +21525,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>3.44</v>
       </c>
       <c r="R110" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF110" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.44</v>
+        <v>3.81</v>
       </c>
       <c r="R112" t="n">
-        <v>2.83</v>
+        <v>2.05</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.72</v>
+        <v>2.15</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>3.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q119" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="R119" t="n">
-        <v>2.58</v>
+        <v>3.74</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23889,10 +23889,10 @@
         <v>0</v>
       </c>
       <c r="AC119" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD119" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE119" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24480,10 +24480,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R125" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25422,7 +25422,7 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P128" t="n">

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>3.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.28</v>
+        <v>2.49</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="R41" t="n">
-        <v>3.03</v>
+        <v>2.63</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="R42" t="n">
-        <v>4.79</v>
+        <v>3.03</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="R54" t="n">
-        <v>3.43</v>
+        <v>2.38</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="R55" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.69</v>
+        <v>2</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="R70" t="n">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="R100" t="n">
-        <v>2.8</v>
+        <v>2.51</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AD100" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.82</v>
+        <v>2.63</v>
       </c>
       <c r="R102" t="n">
-        <v>2.51</v>
+        <v>2.8</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AD102" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R104" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20934,10 +20934,10 @@
         <v>0</v>
       </c>
       <c r="AC104" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD104" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD105" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21525,10 +21525,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21722,10 +21722,10 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.44</v>
+        <v>3</v>
       </c>
       <c r="R110" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="AE110" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF110" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG110" t="n">
         <v>0</v>
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="Q112" t="n">
         <v>3.44</v>
       </c>
-      <c r="Q112" t="n">
-        <v>3.81</v>
-      </c>
       <c r="R112" t="n">
-        <v>2.05</v>
+        <v>2.83</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="AF112" t="n">
-        <v>2.15</v>
+        <v>1.72</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>2.54</v>
+        <v>3.44</v>
       </c>
       <c r="Q114" t="n">
-        <v>3</v>
+        <v>3.81</v>
       </c>
       <c r="R114" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24480,10 +24480,10 @@
         <v>0</v>
       </c>
       <c r="AC122" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD122" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24677,10 +24677,10 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.79</v>
+        <v>3.04</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R129" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="Q130" t="n">
         <v>3.4</v>
       </c>
       <c r="R130" t="n">
-        <v>3.51</v>
+        <v>4.5</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI133"/>
+  <dimension ref="A1:BI140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Asan Mugunghwa</t>
+          <t>Yongin City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hwaseong</t>
+          <t>Suwon Bluewings</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Yongin City</t>
+          <t>Asan Mugunghwa</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Suwon Bluewings</t>
+          <t>Hwaseong</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>3.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="R11" t="n">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.43</v>
+        <v>4.75</v>
       </c>
       <c r="R26" t="n">
-        <v>3.43</v>
+        <v>9.25</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.28</v>
+        <v>2.69</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.75</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>9.25</v>
+        <v>2.4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ospitaletto</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Giana Erminio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Ospitaletto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Giana Erminio</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shinnik</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46109.47916666666</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="39">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="40">
@@ -8234,27 +8234,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8619,7 +8619,7 @@
         <v>0</v>
       </c>
       <c r="BI41" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="42">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="BI42" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="43">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.45833333334</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Shinnik</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46109.5</v>
+        <v>46109.47916666666</v>
       </c>
     </row>
     <row r="46">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>6.26</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.29</v>
+        <v>3.9</v>
       </c>
       <c r="R49" t="n">
-        <v>5.41</v>
+        <v>5.36</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.79</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.4</v>
+        <v>2.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.3</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11287,10 +11287,10 @@
         <v>0</v>
       </c>
       <c r="AE55" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF55" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.8</v>
+        <v>1.57</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.24</v>
+        <v>4.27</v>
       </c>
       <c r="R57" t="n">
-        <v>2.42</v>
+        <v>4.64</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>1.57</v>
+        <v>4.45</v>
       </c>
       <c r="Q59" t="n">
-        <v>4.27</v>
+        <v>3.96</v>
       </c>
       <c r="R59" t="n">
-        <v>4.64</v>
+        <v>1.64</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="Q62" t="n">
-        <v>4.34</v>
+        <v>3.65</v>
       </c>
       <c r="R62" t="n">
-        <v>6.11</v>
+        <v>4.29</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4.45</v>
+        <v>2.49</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.96</v>
+        <v>3.44</v>
       </c>
       <c r="R63" t="n">
-        <v>1.64</v>
+        <v>2.63</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.31</v>
+        <v>3.42</v>
       </c>
       <c r="R65" t="n">
-        <v>2.98</v>
+        <v>2.78</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.65</v>
+        <v>4.15</v>
       </c>
       <c r="R66" t="n">
-        <v>4.29</v>
+        <v>6.26</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13602,7 +13602,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R70" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.16</v>
+        <v>2.4</v>
       </c>
       <c r="Q71" t="n">
         <v>3.3</v>
       </c>
       <c r="R71" t="n">
-        <v>2.21</v>
+        <v>2.88</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Granada CF</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>1.76</v>
+        <v>2</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="R72" t="n">
-        <v>4.84</v>
+        <v>3.43</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14726,7 +14726,7 @@
         <v>0</v>
       </c>
       <c r="BI72" s="3" t="n">
-        <v>46109.51041666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="73">
@@ -14735,27 +14735,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AF73" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14923,7 +14923,7 @@
         <v>0</v>
       </c>
       <c r="BI73" s="3" t="n">
-        <v>46109.51041666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="74">
@@ -14932,12 +14932,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15120,7 +15120,7 @@
         <v>0</v>
       </c>
       <c r="BI74" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="75">
@@ -15129,12 +15129,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15317,7 +15317,7 @@
         <v>0</v>
       </c>
       <c r="BI75" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="76">
@@ -15326,12 +15326,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>La Unión Atlético</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15514,7 +15514,7 @@
         <v>0</v>
       </c>
       <c r="BI76" s="3" t="n">
-        <v>46109.52083333334</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="77">
@@ -15523,27 +15523,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15711,7 +15711,7 @@
         <v>0</v>
       </c>
       <c r="BI77" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="78">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.5</v>
       </c>
     </row>
     <row r="79">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Granada CF</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>4.84</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.51041666666</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.51041666666</v>
       </c>
     </row>
     <row r="81">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>La Unión Atlético</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46109.54166666666</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="82">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="83">
@@ -16705,12 +16705,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.52083333334</v>
       </c>
     </row>
     <row r="84">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="86">
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="87">
@@ -17493,12 +17493,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17681,7 +17681,7 @@
         <v>0</v>
       </c>
       <c r="BI87" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="88">
@@ -17690,27 +17690,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17878,7 +17878,7 @@
         <v>0</v>
       </c>
       <c r="BI88" s="3" t="n">
-        <v>46109.5625</v>
+        <v>46109.54166666666</v>
       </c>
     </row>
     <row r="89">
@@ -17887,12 +17887,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="92">
@@ -18478,12 +18478,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Linares Deportivo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="93">
@@ -18675,12 +18675,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46109.58333333334</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="94">
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="95">
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>3.73</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.5625</v>
       </c>
     </row>
     <row r="96">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46109.60416666666</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="97">
@@ -19463,12 +19463,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Willem II</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19651,7 +19651,7 @@
         <v>0</v>
       </c>
       <c r="BI97" s="3" t="n">
-        <v>46109.61458333334</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="98">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19848,7 +19848,7 @@
         <v>0</v>
       </c>
       <c r="BI98" s="3" t="n">
-        <v>46109.625</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="99">
@@ -19857,27 +19857,27 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20045,7 +20045,7 @@
         <v>0</v>
       </c>
       <c r="BI99" s="3" t="n">
-        <v>46109.625</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="100">
@@ -20054,27 +20054,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Almagro</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Linares Deportivo</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20146,10 +20146,10 @@
         <v>0</v>
       </c>
       <c r="AC100" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD100" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AE100" t="n">
         <v>0</v>
@@ -20242,7 +20242,7 @@
         <v>0</v>
       </c>
       <c r="BI100" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.58333333334</v>
       </c>
     </row>
     <row r="101">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="102">
@@ -20448,27 +20448,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Los Andes</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Temperley</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20540,10 +20540,10 @@
         <v>0</v>
       </c>
       <c r="AC102" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD102" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46109.64583333334</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="103">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>3.73</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.60416666666</v>
       </c>
     </row>
     <row r="104">
@@ -20842,27 +20842,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Willem II</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.61458333334</v>
       </c>
     </row>
     <row r="105">
@@ -21039,27 +21039,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21131,10 +21131,10 @@
         <v>0</v>
       </c>
       <c r="AC105" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD105" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE105" t="n">
         <v>0</v>
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.625</v>
       </c>
     </row>
     <row r="106">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.625</v>
       </c>
     </row>
     <row r="107">
@@ -21433,12 +21433,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Los Andes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Temperley</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21525,10 +21525,10 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AE107" t="n">
         <v>0</v>
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="108">
@@ -21630,27 +21630,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21722,10 +21722,10 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD108" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE108" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46109.66666666666</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="109">
@@ -21827,12 +21827,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Longford Town</t>
+          <t>Almagro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.25</v>
+        <v>2.82</v>
       </c>
       <c r="R109" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21919,16 +21919,16 @@
         <v>0</v>
       </c>
       <c r="AC109" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD109" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AE109" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46109.6875</v>
+        <v>46109.64583333334</v>
       </c>
     </row>
     <row r="110">
@@ -22024,12 +22024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="111">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="112">
@@ -22418,27 +22418,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Sporting Gijón</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.52</v>
+        <v>3.11</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.44</v>
+        <v>2.75</v>
       </c>
       <c r="R112" t="n">
-        <v>2.83</v>
+        <v>2.41</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22510,16 +22510,16 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD112" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE112" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="113">
@@ -22615,12 +22615,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22707,10 +22707,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="114">
@@ -22812,27 +22812,27 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R114" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF114" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46109.70833333334</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="115">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>2.24</v>
+        <v>3.13</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R115" t="n">
-        <v>3.67</v>
+        <v>2.52</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46109.75</v>
+        <v>46109.66666666666</v>
       </c>
     </row>
     <row r="116">
@@ -23206,12 +23206,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Longford Town</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23394,7 +23394,7 @@
         <v>0</v>
       </c>
       <c r="BI116" s="3" t="n">
-        <v>46109.75</v>
+        <v>46109.6875</v>
       </c>
     </row>
     <row r="117">
@@ -23403,27 +23403,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R117" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF117" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23591,7 +23591,7 @@
         <v>0</v>
       </c>
       <c r="BI117" s="3" t="n">
-        <v>46109.8125</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="118">
@@ -23600,12 +23600,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23788,7 +23788,7 @@
         <v>0</v>
       </c>
       <c r="BI118" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="119">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>North Carolina Courage</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bay</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="BI119" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="120">
@@ -23994,27 +23994,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Whitecaps II</t>
+          <t>Sporting Gijón</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Los Angeles II</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24047,13 +24047,13 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="Q120" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="S120" t="n">
         <v>0</v>
@@ -24092,10 +24092,10 @@
         <v>0</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG120" t="n">
         <v>0</v>
@@ -24182,7 +24182,7 @@
         <v>0</v>
       </c>
       <c r="BI120" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="121">
@@ -24191,27 +24191,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Miami FC II</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Rhode Island</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24379,7 +24379,7 @@
         <v>0</v>
       </c>
       <c r="BI121" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.70833333334</v>
       </c>
     </row>
     <row r="122">
@@ -24388,12 +24388,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Pittsburgh Riverhounds</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sporting JAX</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24576,7 +24576,7 @@
         <v>0</v>
       </c>
       <c r="BI122" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.75</v>
       </c>
     </row>
     <row r="123">
@@ -24585,12 +24585,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3.05</v>
+        <v>2.24</v>
       </c>
       <c r="Q123" t="n">
-        <v>2.6</v>
+        <v>2.79</v>
       </c>
       <c r="R123" t="n">
-        <v>2.58</v>
+        <v>3.67</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24677,16 +24677,16 @@
         <v>0</v>
       </c>
       <c r="AC123" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24773,7 +24773,7 @@
         <v>0</v>
       </c>
       <c r="BI123" s="3" t="n">
-        <v>46109.83333333334</v>
+        <v>46109.75</v>
       </c>
     </row>
     <row r="124">
@@ -24782,12 +24782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24970,7 +24970,7 @@
         <v>0</v>
       </c>
       <c r="BI124" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.8125</v>
       </c>
     </row>
     <row r="125">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="126">
@@ -25176,12 +25176,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>North Carolina Courage</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Bay</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.8</v>
+        <v>1.97</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="R126" t="n">
-        <v>3.9</v>
+        <v>3.74</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46109.85416666666</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Whitecaps II</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Los Angeles II</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25561,7 +25561,7 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="128">
@@ -25570,27 +25570,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,17 +25619,17 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q128" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R128" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD128" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -25758,7 +25758,7 @@
         <v>0</v>
       </c>
       <c r="BI128" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="129">
@@ -25767,27 +25767,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Miami FC II</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="Q129" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R129" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
@@ -25955,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="BI129" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="130">
@@ -25964,7 +25964,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Pittsburgh Riverhounds</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Sporting JAX</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26017,13 +26017,13 @@
         </is>
       </c>
       <c r="P130" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="S130" t="n">
         <v>0</v>
@@ -26152,7 +26152,7 @@
         <v>0</v>
       </c>
       <c r="BI130" s="3" t="n">
-        <v>46109.875</v>
+        <v>46109.83333333334</v>
       </c>
     </row>
     <row r="131">
@@ -26161,12 +26161,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>San Diego Wave</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26349,7 +26349,7 @@
         <v>0</v>
       </c>
       <c r="BI131" s="3" t="n">
-        <v>46109.90625</v>
+        <v>46109.85416666666</v>
       </c>
     </row>
     <row r="132">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Sacramento Republic</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>El Paso Locomotive</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q132" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="R132" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="BI132" s="3" t="n">
-        <v>46109.95833333334</v>
+        <v>46109.85416666666</v>
       </c>
     </row>
     <row r="133">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Las Vegas Lights</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Monterey Bay</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,141 +26608,1520 @@
         </is>
       </c>
       <c r="P133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI133" s="3" t="n">
+        <v>46109.85416666666</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Italy Serie C Group B</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Rimini</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Athletic Carpi</t>
+        </is>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>canceled</t>
+        </is>
+      </c>
+      <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI134" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Russia FNL</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Chayka</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Chelyabinsk</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="R135" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI135" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Tulsa Roughnecks</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Phoenix Rising</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R136" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI136" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R137" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI137" s="3" t="n">
+        <v>46109.875</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>San Diego Wave</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI138" s="3" t="n">
+        <v>46109.90625</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Sacramento Republic</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive</t>
+        </is>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N139" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P139" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R139" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI139" s="3" t="n">
+        <v>46109.95833333334</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>23:30</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>USA USL Championship</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Las Vegas Lights</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Monterey Bay</t>
+        </is>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P140" t="n">
         <v>2.35</v>
       </c>
-      <c r="Q133" t="n">
+      <c r="Q140" t="n">
         <v>2.94</v>
       </c>
-      <c r="R133" t="n">
+      <c r="R140" t="n">
         <v>3.01</v>
       </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI133" s="3" t="n">
+      <c r="S140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI140" s="3" t="n">
         <v>46109.97916666666</v>
       </c>
     </row>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,13 +2377,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cheonan City</t>
+          <t>Seongnam</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeonnam Dragons</t>
+          <t>Gimpo Citizen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>3.24</v>
+        <v>2.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="R11" t="n">
-        <v>2.05</v>
+        <v>2.91</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Seongnam</t>
+          <t>Cheonan City</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gimpo Citizen</t>
+          <t>Jeonnam Dragons</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.46</v>
+        <v>3.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.91</v>
+        <v>2.05</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W13" t="n">
         <v>2.34</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="R13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Badalona W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Badalona W</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.01</v>
+        <v>2.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.38</v>
+        <v>2.96</v>
       </c>
       <c r="R18" t="n">
-        <v>2.12</v>
+        <v>2.79</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.84</v>
+        <v>3.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.96</v>
+        <v>3.38</v>
       </c>
       <c r="R22" t="n">
-        <v>2.79</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.75</v>
+        <v>3.43</v>
       </c>
       <c r="R26" t="n">
-        <v>9.25</v>
+        <v>3.43</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.69</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="R27" t="n">
-        <v>2.4</v>
+        <v>9.25</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>3.43</v>
+        <v>2.4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="R49" t="n">
-        <v>5.36</v>
+        <v>4.79</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10105,10 +10105,10 @@
         <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.65</v>
+        <v>2.28</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="R51" t="n">
-        <v>4.79</v>
+        <v>2.98</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.14</v>
+        <v>1.5</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.34</v>
+        <v>4.15</v>
       </c>
       <c r="R52" t="n">
-        <v>3.33</v>
+        <v>6.26</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bijelo Brdo</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Coleraine</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Croatia Zmijavci</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Karlovac 1919</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>4.34</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>6.11</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>4.64</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>6.11</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>4.45</v>
+        <v>2.14</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.96</v>
+        <v>3.34</v>
       </c>
       <c r="R59" t="n">
-        <v>1.64</v>
+        <v>3.33</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>4.64</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="R61" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.65</v>
+        <v>3.24</v>
       </c>
       <c r="R62" t="n">
-        <v>4.29</v>
+        <v>2.42</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Cheltenham Town</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R63" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.38</v>
+        <v>2.69</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="R65" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="n">
-        <v>4.15</v>
+        <v>3.55</v>
       </c>
       <c r="R66" t="n">
-        <v>6.26</v>
+        <v>3.43</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hrvace</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Cibalia</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>1.63</v>
+        <v>2.28</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.29</v>
+        <v>3.35</v>
       </c>
       <c r="R68" t="n">
-        <v>5.41</v>
+        <v>3.03</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,22 +14149,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2</v>
+        <v>2.84</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="R72" t="n">
-        <v>3.43</v>
+        <v>2.38</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,22 +14740,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14833,10 +14833,10 @@
         <v>0</v>
       </c>
       <c r="AE73" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF73" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Bijelo Brdo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Hrvace</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Cibalia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -16907,22 +16907,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Boston Legacy W</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Utah Royals</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,22 +17695,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Boston Legacy W</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Utah Royals</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Novara</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Novara</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alcione</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pro Vercelli</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Alcione</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Pro Vercelli</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Deportivo de La Coruña W</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Deportivo de La Coruña W</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Carolina Core</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Granada W</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Sporting KC II</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granada W</t>
+          <t>St. Louis City II</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ciudad de Bolívar</t>
+          <t>Carolina Core</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22510,10 +22510,10 @@
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
         <v>0</v>
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Almirante Brown</t>
+          <t>New Mexico United</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tristán Suárez</t>
+          <t>Colorado Springs</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2.69</v>
+        <v>3.13</v>
       </c>
       <c r="Q113" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R113" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22707,10 +22707,10 @@
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD113" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Sporting KC II</t>
+          <t>Almirante Brown</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>St. Louis City II</t>
+          <t>Tristán Suárez</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22865,13 +22865,13 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22904,10 +22904,10 @@
         <v>0</v>
       </c>
       <c r="AC114" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD114" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE114" t="n">
         <v>0</v>
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>New Mexico United</t>
+          <t>Ciudad de Bolívar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Colorado Springs</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="Q115" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R115" t="n">
-        <v>2.52</v>
+        <v>2.41</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23101,10 +23101,10 @@
         <v>0</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE115" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Kansas City</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23456,13 +23456,13 @@
         </is>
       </c>
       <c r="P117" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="Q117" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="R117" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S117" t="n">
         <v>0</v>
@@ -23501,10 +23501,10 @@
         <v>0</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AF117" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG117" t="n">
         <v>0</v>
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Detroit City FC</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Charleston Battery</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kansas City</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Detroit City FC</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Charleston Battery</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Hartford Athletic</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Indy Eleven</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>3.67</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Hartford Athletic</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Indy Eleven</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>3.67</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Chattanooga FC</t>
+          <t>Colegiales</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Columbus Crew II</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25032,13 +25032,13 @@
         </is>
       </c>
       <c r="P125" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="Q125" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="S125" t="n">
         <v>0</v>
@@ -25071,10 +25071,10 @@
         <v>0</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AE125" t="n">
         <v>0</v>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Colegiales</t>
+          <t>Chattanooga FC</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Columbus Crew II</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q128" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="R128" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25662,10 +25662,10 @@
         <v>0</v>
       </c>
       <c r="AC128" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD128" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AE128" t="n">
         <v>0</v>
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Brooklyn FC</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Copiapó</t>
+          <t>Louisville City</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tampa Bay Rowdies</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Loudoun United</t>
+          <t>Copiapó</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26411,13 +26411,13 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q132" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R132" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S132" t="n">
         <v>0</v>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Brooklyn FC</t>
+          <t>Tampa Bay Rowdies</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Louisville City</t>
+          <t>Loudoun United</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Tulsa Roughnecks</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Athletic Carpi</t>
+          <t>Phoenix Rising</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26801,17 +26801,17 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>
@@ -26954,22 +26954,22 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>USA USL Championship</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>Oakland Roots</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Chelyabinsk</t>
+          <t>Orange County SC</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,13 +27002,13 @@
         </is>
       </c>
       <c r="P135" t="n">
-        <v>3.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q135" t="n">
-        <v>3.28</v>
+        <v>3.4</v>
       </c>
       <c r="R135" t="n">
-        <v>2.42</v>
+        <v>3.51</v>
       </c>
       <c r="S135" t="n">
         <v>0</v>
@@ -27151,22 +27151,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tulsa Roughnecks</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Phoenix Rising</t>
+          <t>Chelyabinsk</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -27199,13 +27199,13 @@
         </is>
       </c>
       <c r="P136" t="n">
-        <v>1.79</v>
+        <v>3.04</v>
       </c>
       <c r="Q136" t="n">
-        <v>3.4</v>
+        <v>3.28</v>
       </c>
       <c r="R136" t="n">
-        <v>4.5</v>
+        <v>2.42</v>
       </c>
       <c r="S136" t="n">
         <v>0</v>
@@ -27348,22 +27348,22 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>USA USL Championship</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Oakland Roots</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orange County SC</t>
+          <t>Athletic Carpi</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -27392,17 +27392,17 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q137" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="S137" t="n">
         <v>0</v>

--- a/jogos_2026-03-28.xlsx
+++ b/jogos_2026-03-28.xlsx
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3</v>
+      </c>
+      <c r="R4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC4" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R4" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Rockdale City Suns</t>
+          <t>Pohang Steelers</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sydney United</t>
+          <t>Gangwon</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>UNSW</t>
+          <t>Rockdale City Suns</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>St George City FA</t>
+          <t>Sydney United</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South Korea K League 1</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pohang Steelers</t>
+          <t>UNSW</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gangwon</t>
+          <t>St George City FA</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Korea K League 2</t>
+          <t>Australia New South Wales NPL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ansan Greeners</t>
+          <t>St. George Saints</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gyeongnam</t>
+          <t>NWS Spirit</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Australia New South Wales NPL</t>
+          <t>South Korea K League 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>St. George Saints</t>
+          <t>Ansan Greeners</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NWS Spirit</t>
+          <t>Gyeongnam</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.86</v>
+        <v>2.89</v>
       </c>
       <c r="R11" t="n">
-        <v>2.91</v>
+        <v>3.05</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.24</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="X12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD12" t="n">
         <v>3.3</v>
       </c>
-      <c r="R12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
       <c r="AE12" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>3.18</v>
       </c>
       <c r="R13" t="n">
         <v>3.45</v>
@@ -3174,70 +3174,70 @@
         <v>10.3</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Haugesund W</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>Spartak Kostroma</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,79 +3756,79 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spartak Kostroma</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Fortuna Ålesund</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Fortuna Ålesund</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liverpool Women</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.01</v>
+        <v>2.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>2.41</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Liverpool Women</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -4983,10 +4983,10 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Haugesund W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.62</v>
+        <v>4.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.69</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.43</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>3.43</v>
+        <v>2.4</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.69</v>
+        <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="R28" t="n">
-        <v>2.4</v>
+        <v>3.43</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5968,10 +5968,10 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG28" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Livorno</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Manchester City Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Manchester City Women</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Livorno</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jarun</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eskilstuna United</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vittsjö</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Jarun</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Eskilstuna United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Vittsjö</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="R45" t="n">
-        <v>3.96</v>
+        <v>3.69</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Alcochetense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>Louletano</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,79 +9666,79 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>6.27</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
@@ -9780,19 +9780,19 @@
         <v>0</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>1.77</v>
+        <v>2.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="R48" t="n">
-        <v>4.29</v>
+        <v>3.03</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -9908,10 +9908,10 @@
         <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="AF48" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AG48" t="n">
         <v>0</v>
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Espanyol W</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>4.79</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,133 +10257,133 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
       </c>
       <c r="AP50" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR50" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT50" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU50" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW50" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AX50" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY50" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ50" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BA50" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BB50" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD50" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF50" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Croatia Zmijavci</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Karlovac 1919</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Reading</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q52" t="n">
-        <v>4.15</v>
+        <v>3.34</v>
       </c>
       <c r="R52" t="n">
-        <v>6.26</v>
+        <v>3.33</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mansfield Town</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>5.36</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF54" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Coleraine</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>4.45</v>
+        <v>2.41</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.96</v>
+        <v>3.17</v>
       </c>
       <c r="R55" t="n">
-        <v>1.64</v>
+        <v>2.8</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="Q56" t="n">
-        <v>4.34</v>
+        <v>4.15</v>
       </c>
       <c r="R56" t="n">
-        <v>6.11</v>
+        <v>6.26</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alcochetense</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Louletano</t>
+          <t>Mansfield Town</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>5.36</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11878,10 +11878,10 @@
         <v>0</v>
       </c>
       <c r="AE58" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF58" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.34</v>
+        <v>3.31</v>
       </c>
       <c r="R59" t="n">
-        <v>3.33</v>
+        <v>2.98</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,133 +12227,133 @@
         </is>
       </c>
       <c r="P60" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S60" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W60" t="n">
+        <v>3</v>
+      </c>
+      <c r="X60" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN60" t="n">
         <v>1.57</v>
       </c>
-      <c r="Q60" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="R60" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>0</v>
-      </c>
       <c r="AO60" t="n">
         <v>0</v>
       </c>
       <c r="AP60" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AR60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS60" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT60" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AU60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="AV60" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AW60" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX60" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AY60" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BA60" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BB60" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD60" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Espanyol W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,133 +12424,133 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="Q61" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R61" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="S61" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U61" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="X61" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y61" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z61" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC61" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD61" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AE61" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF61" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG61" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY61" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA61" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB61" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC61" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BD61" t="n">
         <v>3.3</v>
       </c>
-      <c r="R61" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0</v>
-      </c>
-      <c r="T61" t="n">
-        <v>0</v>
-      </c>
-      <c r="U61" t="n">
-        <v>0</v>
-      </c>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="n">
-        <v>0</v>
-      </c>
-      <c r="X61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY61" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC61" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD61" t="n">
-        <v>0</v>
-      </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,133 +12621,133 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
       </c>
       <c r="AP62" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR62" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AS62" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AT62" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU62" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV62" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AW62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX62" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AY62" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BA62" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cheltenham Town</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,133 +12818,133 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
       </c>
       <c r="AP63" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR63" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS63" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT63" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU63" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV63" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AW63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX63" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BA63" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BB63" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC63" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BD63" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.69</v>
+        <v>2.26</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="R65" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,133 +13409,133 @@
         </is>
       </c>
       <c r="P66" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R66" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="S66" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W66" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X66" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN66" t="n">
         <v>2</v>
       </c>
-      <c r="Q66" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="R66" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="S66" t="n">
-        <v>0</v>
-      </c>
-      <c r="T66" t="n">
-        <v>0</v>
-      </c>
-      <c r="U66" t="n">
-        <v>0</v>
-      </c>
-      <c r="V66" t="n">
-        <v>0</v>
-      </c>
-      <c r="W66" t="n">
-        <v>0</v>
-      </c>
-      <c r="X66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>0</v>
-      </c>
       <c r="AO66" t="n">
         <v>0</v>
       </c>
       <c r="AP66" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR66" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AS66" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT66" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU66" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AV66" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AW66" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AX66" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY66" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BA66" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC66" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD66" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF66" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
      